--- a/SI/Hydro..RecycleProcessFromArmita.xlsx
+++ b/SI/Hydro..RecycleProcessFromArmita.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="7070"/>
+    <workbookView windowWidth="18340" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -147,7 +147,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,13 +176,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -327,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,12 +432,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,148 +679,148 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -1200,15 +1187,15 @@
   <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="15.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="7.90909090909091" customWidth="1"/>
-    <col min="7" max="7" width="9.72727272727273" customWidth="1"/>
+    <col min="1" max="1" width="11.725" customWidth="1"/>
+    <col min="3" max="3" width="12.8166666666667" customWidth="1"/>
+    <col min="5" max="5" width="15.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.90833333333333" customWidth="1"/>
+    <col min="7" max="7" width="9.725" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="39.9090909090909" customWidth="1"/>
+    <col min="9" max="9" width="39.9083333333333" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="8.81818181818182" customWidth="1"/>
+    <col min="11" max="11" width="8.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
@@ -1313,7 +1300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="28" spans="1:15">
+    <row r="4" spans="1:15">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -1548,7 +1535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="28" spans="1:15">
+    <row r="9" spans="1:15">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -1658,8 +1645,8 @@
     </row>
     <row r="13" spans="2:15">
       <c r="B13">
-        <f>B3*B5*B6*B7*B8*B9</f>
-        <v>0.6561</v>
+        <f>B9</f>
+        <v>0.9</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1671,16 +1658,16 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <f>F3*F5*F6*F7*F8*F9</f>
-        <v>0.6561</v>
+        <f>F9</f>
+        <v>0.9</v>
       </c>
       <c r="G13">
-        <f t="shared" ref="G13:L13" si="1">G3*G5*G6*G7*G8*G9</f>
-        <v>0.6561</v>
+        <f>G9</f>
+        <v>0.9</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
-        <v>0.6561</v>
+        <f>H9</f>
+        <v>0.9</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1692,19 +1679,19 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
+        <f>L9</f>
         <v>0.9</v>
       </c>
       <c r="M13">
-        <f>M3*M5*M6*M7*M8*M9</f>
+        <f>M9</f>
         <v>0.98</v>
       </c>
       <c r="N13">
-        <f>N3*N5*N6*N7*N8*N9</f>
+        <f>N9</f>
         <v>0.98</v>
       </c>
       <c r="O13">
-        <f>O3*O5*O6*O7*O8*O9</f>
+        <f>O9</f>
         <v>0.98</v>
       </c>
     </row>
@@ -1764,15 +1751,15 @@
       </c>
       <c r="F19" s="9">
         <f>G13</f>
-        <v>0.6561</v>
+        <v>0.9</v>
       </c>
       <c r="G19" s="9">
         <f>F13</f>
-        <v>0.6561</v>
+        <v>0.9</v>
       </c>
       <c r="H19" s="9">
         <f>B13</f>
-        <v>0.6561</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
